--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46313</v>
+        <v>46320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/action-plan-template/action-plan-template-expert.xlsx
+++ b/templates/action-plan-template/action-plan-template-expert.xlsx
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
